--- a/data/06延伸資料/縣市人口資料含北中南區域彙整_2017-2026_中.xlsx
+++ b/data/06延伸資料/縣市人口資料含北中南區域彙整_2017-2026_中.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\260321_nNiseproj\data\06延伸資料\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5EE8FA-499D-4380-A0D1-F7507897C0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="510" windowWidth="17950" windowHeight="6240" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="各縣市" sheetId="1" r:id="rId1"/>
@@ -19,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="43">
   <si>
     <t>時間</t>
   </si>
@@ -153,11 +159,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,12 +199,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -207,6 +216,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -494,21 +511,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H221"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,7 +551,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46054</v>
       </c>
@@ -560,7 +577,7 @@
         <v>1969.84</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46054</v>
       </c>
@@ -586,7 +603,7 @@
         <v>8956.89</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46054</v>
       </c>
@@ -612,7 +629,7 @@
         <v>1929.24</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46054</v>
       </c>
@@ -638,7 +655,7 @@
         <v>1295.05</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46054</v>
       </c>
@@ -664,7 +681,7 @@
         <v>844.68</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46054</v>
       </c>
@@ -690,7 +707,7 @@
         <v>919.96</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46054</v>
       </c>
@@ -716,7 +733,7 @@
         <v>209.4</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46054</v>
       </c>
@@ -742,7 +759,7 @@
         <v>418.36</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46054</v>
       </c>
@@ -768,7 +785,7 @@
         <v>291.48</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46054</v>
       </c>
@@ -794,7 +811,7 @@
         <v>1124.3699999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46054</v>
       </c>
@@ -820,7 +837,7 @@
         <v>113.84</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46054</v>
       </c>
@@ -846,7 +863,7 @@
         <v>503.28</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>46054</v>
       </c>
@@ -872,7 +889,7 @@
         <v>248.14</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>46054</v>
       </c>
@@ -898,7 +915,7 @@
         <v>281.43</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>46054</v>
       </c>
@@ -924,7 +941,7 @@
         <v>59.2</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>46054</v>
       </c>
@@ -950,7 +967,7 @@
         <v>67.44</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>46054</v>
       </c>
@@ -976,7 +993,7 @@
         <v>840.81</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>46054</v>
       </c>
@@ -1002,7 +1019,7 @@
         <v>2706.48</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>46054</v>
       </c>
@@ -1028,7 +1045,7 @@
         <v>4377.82</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46054</v>
       </c>
@@ -1054,7 +1071,7 @@
         <v>4356.96</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46054</v>
       </c>
@@ -1080,7 +1097,7 @@
         <v>915.91</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>46054</v>
       </c>
@@ -1106,7 +1123,7 @@
         <v>473.3</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
@@ -1132,7 +1149,7 @@
         <v>1970.62</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
@@ -1158,7 +1175,7 @@
         <v>8975.39</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -1184,7 +1201,7 @@
         <v>1928.91</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
@@ -1210,7 +1227,7 @@
         <v>1295.08</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1236,7 +1253,7 @@
         <v>845.24</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
@@ -1262,7 +1279,7 @@
         <v>920.88</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
@@ -1288,7 +1305,7 @@
         <v>209.62</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
@@ -1314,7 +1331,7 @@
         <v>418.37</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
@@ -1340,7 +1357,7 @@
         <v>291.8</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
@@ -1366,7 +1383,7 @@
         <v>1126.4100000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
@@ -1392,7 +1409,7 @@
         <v>113.94</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -1418,7 +1435,7 @@
         <v>504.32</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -1444,7 +1461,7 @@
         <v>248.57</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>34</v>
       </c>
@@ -1470,7 +1487,7 @@
         <v>281.83</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>34</v>
       </c>
@@ -1496,7 +1513,7 @@
         <v>59.26</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>34</v>
       </c>
@@ -1522,7 +1539,7 @@
         <v>67.58</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>34</v>
       </c>
@@ -1548,7 +1565,7 @@
         <v>841.18</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1574,7 +1591,7 @@
         <v>2710.45</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1600,7 +1617,7 @@
         <v>4375.6899999999996</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>34</v>
       </c>
@@ -1626,7 +1643,7 @@
         <v>4358.01</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>34</v>
       </c>
@@ -1652,7 +1669,7 @@
         <v>918.61</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>34</v>
       </c>
@@ -1678,7 +1695,7 @@
         <v>472.95</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>35</v>
       </c>
@@ -1704,7 +1721,7 @@
         <v>1971.68</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>35</v>
       </c>
@@ -1730,7 +1747,7 @@
         <v>9164.36</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>35</v>
       </c>
@@ -1756,7 +1773,7 @@
         <v>1915.43</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>35</v>
       </c>
@@ -1782,7 +1799,7 @@
         <v>1291.53</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>35</v>
       </c>
@@ -1808,7 +1825,7 @@
         <v>848.06</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>35</v>
       </c>
@@ -1834,7 +1851,7 @@
         <v>925.24</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>35</v>
       </c>
@@ -1860,7 +1877,7 @@
         <v>209.56</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>35</v>
       </c>
@@ -1886,7 +1903,7 @@
         <v>416.55</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>35</v>
       </c>
@@ -1912,7 +1929,7 @@
         <v>292.73</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>35</v>
       </c>
@@ -1938,7 +1955,7 @@
         <v>1140.8</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>35</v>
       </c>
@@ -1964,7 +1981,7 @@
         <v>115.01</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>35</v>
       </c>
@@ -1990,7 +2007,7 @@
         <v>510.08</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>35</v>
       </c>
@@ -2016,7 +2033,7 @@
         <v>251.51</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>35</v>
       </c>
@@ -2042,7 +2059,7 @@
         <v>284.35000000000002</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>35</v>
       </c>
@@ -2068,7 +2085,7 @@
         <v>59.8</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>35</v>
       </c>
@@ -2094,7 +2111,7 @@
         <v>68.14</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>35</v>
       </c>
@@ -2120,7 +2137,7 @@
         <v>850.52</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>35</v>
       </c>
@@ -2146,7 +2163,7 @@
         <v>2722.54</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>35</v>
       </c>
@@ -2172,7 +2189,7 @@
         <v>4390.12</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>35</v>
       </c>
@@ -2198,7 +2215,7 @@
         <v>4367.75</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>35</v>
       </c>
@@ -2224,7 +2241,7 @@
         <v>946.89</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>35</v>
       </c>
@@ -2250,7 +2267,7 @@
         <v>484.38</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>36</v>
       </c>
@@ -2276,7 +2293,7 @@
         <v>1968.81</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>36</v>
       </c>
@@ -2302,7 +2319,7 @@
         <v>9241.68</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>36</v>
       </c>
@@ -2328,7 +2345,7 @@
         <v>1898.06</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>36</v>
       </c>
@@ -2354,7 +2371,7 @@
         <v>1284.8900000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>36</v>
       </c>
@@ -2380,7 +2397,7 @@
         <v>848.65</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>36</v>
       </c>
@@ -2406,7 +2423,7 @@
         <v>927.45</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>36</v>
       </c>
@@ -2432,7 +2449,7 @@
         <v>209.87</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>36</v>
       </c>
@@ -2458,7 +2475,7 @@
         <v>412.8</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>36</v>
       </c>
@@ -2484,7 +2501,7 @@
         <v>293.67</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -2510,7 +2527,7 @@
         <v>1153.25</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>36</v>
       </c>
@@ -2536,7 +2553,7 @@
         <v>116.18</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>36</v>
       </c>
@@ -2562,7 +2579,7 @@
         <v>510.89</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>36</v>
       </c>
@@ -2588,7 +2605,7 @@
         <v>254.54</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>36</v>
       </c>
@@ -2614,7 +2631,7 @@
         <v>286.42</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>36</v>
       </c>
@@ -2640,7 +2657,7 @@
         <v>60.18</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>36</v>
       </c>
@@ -2666,7 +2683,7 @@
         <v>68.59</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>36</v>
       </c>
@@ -2692,7 +2709,7 @@
         <v>849.25</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>36</v>
       </c>
@@ -2718,7 +2735,7 @@
         <v>2728.67</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>36</v>
       </c>
@@ -2744,7 +2761,7 @@
         <v>4382.75</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>36</v>
       </c>
@@ -2770,7 +2787,7 @@
         <v>4391.1899999999996</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>36</v>
       </c>
@@ -2796,7 +2813,7 @@
         <v>950.5</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>36</v>
       </c>
@@ -2822,7 +2839,7 @@
         <v>487.47</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>37</v>
       </c>
@@ -2848,7 +2865,7 @@
         <v>1946.61</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>37</v>
       </c>
@@ -2874,7 +2891,7 @@
         <v>9126.8700000000008</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>37</v>
       </c>
@@ -2900,7 +2917,7 @@
         <v>1868.59</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>37</v>
       </c>
@@ -2926,7 +2943,7 @@
         <v>1270.7</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>37</v>
       </c>
@@ -2952,7 +2969,7 @@
         <v>845.48</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>37</v>
       </c>
@@ -2978,7 +2995,7 @@
         <v>924.21</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>37</v>
       </c>
@@ -3004,7 +3021,7 @@
         <v>209.49</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>37</v>
       </c>
@@ -3030,7 +3047,7 @@
         <v>406.65</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>37</v>
       </c>
@@ -3056,7 +3073,7 @@
         <v>293.98</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>37</v>
       </c>
@@ -3082,7 +3099,7 @@
         <v>1159.01</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>37</v>
       </c>
@@ -3108,7 +3125,7 @@
         <v>116.79</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>37</v>
       </c>
@@ -3134,7 +3151,7 @@
         <v>514.47</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>37</v>
       </c>
@@ -3160,7 +3177,7 @@
         <v>256.43</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>37</v>
       </c>
@@ -3186,7 +3203,7 @@
         <v>287.76</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>37</v>
       </c>
@@ -3212,7 +3229,7 @@
         <v>60.47</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>37</v>
       </c>
@@ -3238,7 +3255,7 @@
         <v>68.900000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>37</v>
       </c>
@@ -3264,7 +3281,7 @@
         <v>845.18</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>37</v>
       </c>
@@ -3290,7 +3307,7 @@
         <v>2723.18</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>37</v>
       </c>
@@ -3316,7 +3333,7 @@
         <v>4344.33</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>37</v>
       </c>
@@ -3342,7 +3359,7 @@
         <v>4380.2</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>37</v>
       </c>
@@ -3368,7 +3385,7 @@
         <v>931.68</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>37</v>
       </c>
@@ -3394,7 +3411,7 @@
         <v>485.52</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>38</v>
       </c>
@@ -3420,7 +3437,7 @@
         <v>1952.73</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>38</v>
       </c>
@@ -3446,7 +3463,7 @@
         <v>9287.7000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>38</v>
       </c>
@@ -3472,7 +3489,7 @@
         <v>1861.16</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>38</v>
       </c>
@@ -3498,7 +3515,7 @@
         <v>1270.26</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>38</v>
       </c>
@@ -3524,7 +3541,7 @@
         <v>849.61</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>38</v>
       </c>
@@ -3550,7 +3567,7 @@
         <v>929.82</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>38</v>
       </c>
@@ -3576,7 +3593,7 @@
         <v>210.25</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>38</v>
       </c>
@@ -3602,7 +3619,7 @@
         <v>403.2</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>38</v>
       </c>
@@ -3628,7 +3645,7 @@
         <v>295.64999999999998</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>38</v>
       </c>
@@ -3654,7 +3671,7 @@
         <v>1168.4100000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>38</v>
       </c>
@@ -3680,7 +3697,7 @@
         <v>118.08</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>38</v>
       </c>
@@ -3706,7 +3723,7 @@
         <v>519.15</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>38</v>
       </c>
@@ -3732,7 +3749,7 @@
         <v>259.14</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>38</v>
       </c>
@@ -3758,7 +3775,7 @@
         <v>289.83</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>38</v>
       </c>
@@ -3784,7 +3801,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>38</v>
       </c>
@@ -3810,7 +3827,7 @@
         <v>69.430000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>38</v>
       </c>
@@ -3836,7 +3853,7 @@
         <v>838.22</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>38</v>
       </c>
@@ -3862,7 +3879,7 @@
         <v>2741.64</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>38</v>
       </c>
@@ -3888,7 +3905,7 @@
         <v>4345.93</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>38</v>
       </c>
@@ -3914,7 +3931,7 @@
         <v>4410.2299999999996</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>38</v>
       </c>
@@ -3940,7 +3957,7 @@
         <v>933.29</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>38</v>
       </c>
@@ -3966,7 +3983,7 @@
         <v>473.78</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>39</v>
       </c>
@@ -3992,7 +4009,7 @@
         <v>1963.86</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>39</v>
       </c>
@@ -4018,7 +4035,7 @@
         <v>9574.76</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>39</v>
       </c>
@@ -4044,7 +4061,7 @@
         <v>1858.22</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>39</v>
       </c>
@@ -4070,7 +4087,7 @@
         <v>1273.55</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>39</v>
       </c>
@@ -4096,7 +4113,7 @@
         <v>855.48</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>39</v>
       </c>
@@ -4122,7 +4139,7 @@
         <v>937.02</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>39</v>
       </c>
@@ -4148,7 +4165,7 @@
         <v>211.36</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>39</v>
       </c>
@@ -4174,7 +4191,7 @@
         <v>399.83</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>39</v>
       </c>
@@ -4200,7 +4217,7 @@
         <v>298.07</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>39</v>
       </c>
@@ -4226,7 +4243,7 @@
         <v>1178.96</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>39</v>
       </c>
@@ -4252,7 +4269,7 @@
         <v>119.53</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>39</v>
       </c>
@@ -4278,7 +4295,7 @@
         <v>524.37</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>39</v>
       </c>
@@ -4304,7 +4321,7 @@
         <v>262.38</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>39</v>
       </c>
@@ -4330,7 +4347,7 @@
         <v>292.79000000000002</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>39</v>
       </c>
@@ -4356,7 +4373,7 @@
         <v>61.24</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>39</v>
       </c>
@@ -4382,7 +4399,7 @@
         <v>70.08</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>39</v>
       </c>
@@ -4408,7 +4425,7 @@
         <v>835.16</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>39</v>
       </c>
@@ -4434,7 +4451,7 @@
         <v>2768.76</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>39</v>
       </c>
@@ -4460,7 +4477,7 @@
         <v>4334.1400000000003</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>39</v>
       </c>
@@ -4486,7 +4503,7 @@
         <v>4431.53</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>39</v>
       </c>
@@ -4512,7 +4529,7 @@
         <v>927.08</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>39</v>
       </c>
@@ -4538,7 +4555,7 @@
         <v>461.08</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>40</v>
       </c>
@@ -4564,7 +4581,7 @@
         <v>1957.89</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>40</v>
       </c>
@@ -4590,7 +4607,7 @@
         <v>9731.58</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>40</v>
       </c>
@@ -4616,7 +4633,7 @@
         <v>1842.03</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>40</v>
       </c>
@@ -4642,7 +4659,7 @@
         <v>1271.06</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>40</v>
       </c>
@@ -4668,7 +4685,7 @@
         <v>858.21</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>40</v>
       </c>
@@ -4694,7 +4711,7 @@
         <v>939.48</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>40</v>
       </c>
@@ -4720,7 +4737,7 @@
         <v>211.87</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>40</v>
       </c>
@@ -4746,7 +4763,7 @@
         <v>395.04</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>40</v>
       </c>
@@ -4772,7 +4789,7 @@
         <v>299.64999999999998</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>40</v>
       </c>
@@ -4798,7 +4815,7 @@
         <v>1184.67</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>40</v>
       </c>
@@ -4824,7 +4841,7 @@
         <v>120.33</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>40</v>
       </c>
@@ -4850,7 +4867,7 @@
         <v>527.79999999999995</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>40</v>
       </c>
@@ -4876,7 +4893,7 @@
         <v>264.29000000000002</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>40</v>
       </c>
@@ -4902,7 +4919,7 @@
         <v>295.14</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>40</v>
       </c>
@@ -4928,7 +4945,7 @@
         <v>61.67</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>40</v>
       </c>
@@ -4954,7 +4971,7 @@
         <v>70.489999999999995</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>40</v>
       </c>
@@ -4980,7 +4997,7 @@
         <v>829.29</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>40</v>
       </c>
@@ -5006,7 +5023,7 @@
         <v>2778.67</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>40</v>
       </c>
@@ -5032,7 +5049,7 @@
         <v>4309.09</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>40</v>
       </c>
@@ -5058,7 +5075,7 @@
         <v>4459.6000000000004</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>40</v>
       </c>
@@ -5084,7 +5101,7 @@
         <v>924.36</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>40</v>
       </c>
@@ -5110,7 +5127,7 @@
         <v>454.48</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>41</v>
       </c>
@@ -5136,7 +5153,7 @@
         <v>1946.69</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>41</v>
       </c>
@@ -5162,7 +5179,7 @@
         <v>9818.16</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>41</v>
       </c>
@@ -5188,7 +5205,7 @@
         <v>1818.96</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>41</v>
       </c>
@@ -5214,7 +5231,7 @@
         <v>1265.93</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>41</v>
       </c>
@@ -5240,7 +5257,7 @@
         <v>859.55</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>41</v>
       </c>
@@ -5266,7 +5283,7 @@
         <v>939.59</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>41</v>
       </c>
@@ -5292,7 +5309,7 @@
         <v>212.36</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>41</v>
       </c>
@@ -5318,7 +5335,7 @@
         <v>390.19</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>41</v>
       </c>
@@ -5344,7 +5361,7 @@
         <v>301.52</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>41</v>
       </c>
@@ -5370,7 +5387,7 @@
         <v>1189.3399999999999</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>41</v>
       </c>
@@ -5396,7 +5413,7 @@
         <v>121.04</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>41</v>
       </c>
@@ -5422,7 +5439,7 @@
         <v>531.46</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>41</v>
       </c>
@@ -5448,7 +5465,7 @@
         <v>266.37</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>41</v>
       </c>
@@ -5474,7 +5491,7 @@
         <v>297.38</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>41</v>
       </c>
@@ -5500,7 +5517,7 @@
         <v>62.28</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>41</v>
       </c>
@@ -5526,7 +5543,7 @@
         <v>70.86</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>41</v>
       </c>
@@ -5552,7 +5569,7 @@
         <v>823.24</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>41</v>
       </c>
@@ -5578,7 +5595,7 @@
         <v>2788.17</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>41</v>
       </c>
@@ -5604,7 +5621,7 @@
         <v>4278.67</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>41</v>
       </c>
@@ -5630,7 +5647,7 @@
         <v>4475.12</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>41</v>
       </c>
@@ -5656,7 +5673,7 @@
         <v>918.35</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>41</v>
       </c>
@@ -5682,7 +5699,7 @@
         <v>453.33</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>42</v>
       </c>
@@ -5708,7 +5725,7 @@
         <v>1942.29</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>42</v>
       </c>
@@ -5734,7 +5751,7 @@
         <v>9872.19</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>42</v>
       </c>
@@ -5760,7 +5777,7 @@
         <v>1792.06</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>42</v>
       </c>
@@ -5786,7 +5803,7 @@
         <v>1258.33</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>42</v>
       </c>
@@ -5812,7 +5829,7 @@
         <v>860.78</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>42</v>
       </c>
@@ -5838,7 +5855,7 @@
         <v>940.74</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>42</v>
       </c>
@@ -5864,7 +5881,7 @@
         <v>213.01</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>42</v>
       </c>
@@ -5890,7 +5907,7 @@
         <v>386.8</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>42</v>
       </c>
@@ -5916,7 +5933,7 @@
         <v>304.24</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>42</v>
       </c>
@@ -5942,7 +5959,7 @@
         <v>1193.6500000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>42</v>
       </c>
@@ -5968,7 +5985,7 @@
         <v>122.02</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>42</v>
       </c>
@@ -5994,7 +6011,7 @@
         <v>534.83000000000004</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>42</v>
       </c>
@@ -6020,7 +6037,7 @@
         <v>268.52999999999997</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>42</v>
       </c>
@@ -6046,7 +6063,7 @@
         <v>299.01</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>42</v>
       </c>
@@ -6072,7 +6089,7 @@
         <v>62.45</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>42</v>
       </c>
@@ -6098,7 +6115,7 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>42</v>
       </c>
@@ -6124,7 +6141,7 @@
         <v>820.35</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>42</v>
       </c>
@@ -6150,7 +6167,7 @@
         <v>2797.99</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>42</v>
       </c>
@@ -6176,7 +6193,7 @@
         <v>4235.4399999999996</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>42</v>
       </c>
@@ -6202,7 +6219,7 @@
         <v>4488.05</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>42</v>
       </c>
@@ -6228,7 +6245,7 @@
         <v>906.37</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>42</v>
       </c>
@@ -6262,21 +6279,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H41"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" style="1"/>
-    <col min="3" max="3" width="21.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="1" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6302,9 +6319,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2">
-        <v>46054</v>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>2026</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>30</v>
@@ -6328,9 +6345,9 @@
         <v>1454.37</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2">
-        <v>46054</v>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2026</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>31</v>
@@ -6354,9 +6371,9 @@
         <v>544.79999999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2">
-        <v>46054</v>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>2026</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>32</v>
@@ -6380,9 +6397,9 @@
         <v>618.26</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2">
-        <v>46054</v>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>2026</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>33</v>
@@ -6406,9 +6423,9 @@
         <v>63.88</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>34</v>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2025</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>30</v>
@@ -6432,9 +6449,9 @@
         <v>1455.33</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>34</v>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>2025</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>31</v>
@@ -6458,9 +6475,9 @@
         <v>545.23</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>34</v>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>2025</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>32</v>
@@ -6484,9 +6501,9 @@
         <v>618.86</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>34</v>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2025</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>33</v>
@@ -6510,9 +6527,9 @@
         <v>63.99</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>35</v>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>2024</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>30</v>
@@ -6536,9 +6553,9 @@
         <v>1460.42</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
-        <v>35</v>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>2024</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>31</v>
@@ -6562,9 +6579,9 @@
         <v>547.25</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
-        <v>35</v>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>2024</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>32</v>
@@ -6588,9 +6605,9 @@
         <v>622.20000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1" t="s">
-        <v>35</v>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>2024</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>33</v>
@@ -6614,9 +6631,9 @@
         <v>64.540000000000006</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1" t="s">
-        <v>36</v>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>2023</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>30</v>
@@ -6640,9 +6657,9 @@
         <v>1458.97</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1" t="s">
-        <v>36</v>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>2023</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>31</v>
@@ -6666,9 +6683,9 @@
         <v>547.84</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="1" t="s">
-        <v>36</v>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>2023</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>32</v>
@@ -6692,9 +6709,9 @@
         <v>624.26</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>2023</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>33</v>
@@ -6718,9 +6735,9 @@
         <v>64.959999999999994</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>2022</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>30</v>
@@ -6744,9 +6761,9 @@
         <v>1441.68</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="1" t="s">
-        <v>37</v>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>2022</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>31</v>
@@ -6770,9 +6787,9 @@
         <v>546.16999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="1" t="s">
-        <v>37</v>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>2022</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>32</v>
@@ -6796,9 +6813,9 @@
         <v>623.21</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="1" t="s">
-        <v>37</v>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>2022</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>33</v>
@@ -6822,9 +6839,9 @@
         <v>65.260000000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="1" t="s">
-        <v>38</v>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>2021</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>30</v>
@@ -6848,9 +6865,9 @@
         <v>1448.01</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="1" t="s">
-        <v>38</v>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>2021</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>31</v>
@@ -6874,9 +6891,9 @@
         <v>548.41</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="1" t="s">
-        <v>38</v>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>2021</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>32</v>
@@ -6900,9 +6917,9 @@
         <v>626.95000000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="1" t="s">
-        <v>38</v>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>2021</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>33</v>
@@ -6926,9 +6943,9 @@
         <v>65.66</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="1" t="s">
-        <v>39</v>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>2020</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>30</v>
@@ -6952,9 +6969,9 @@
         <v>1461.23</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="1" t="s">
-        <v>39</v>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>2020</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>31</v>
@@ -6978,9 +6995,9 @@
         <v>551.80999999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="1" t="s">
-        <v>39</v>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>2020</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>32</v>
@@ -7004,9 +7021,9 @@
         <v>631.89</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="1" t="s">
-        <v>39</v>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>2020</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>33</v>
@@ -7030,9 +7047,9 @@
         <v>66.260000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="1" t="s">
-        <v>40</v>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>2019</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>30</v>
@@ -7056,9 +7073,9 @@
         <v>1461.72</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="1" t="s">
-        <v>40</v>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>2019</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>31</v>
@@ -7082,9 +7099,9 @@
         <v>552.87</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="1" t="s">
-        <v>40</v>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>2019</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>32</v>
@@ -7108,9 +7125,9 @@
         <v>634.32000000000005</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>2019</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>33</v>
@@ -7134,9 +7151,9 @@
         <v>66.680000000000007</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>2018</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
@@ -7160,9 +7177,9 @@
         <v>1456.9</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="1" t="s">
-        <v>41</v>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>2018</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>31</v>
@@ -7186,9 +7203,9 @@
         <v>553.32000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="1" t="s">
-        <v>41</v>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>2018</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>32</v>
@@ -7212,9 +7229,9 @@
         <v>635.67999999999995</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="1" t="s">
-        <v>41</v>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>2018</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>33</v>
@@ -7238,9 +7255,9 @@
         <v>67.150000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="1" t="s">
-        <v>42</v>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>2017</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>30</v>
@@ -7264,9 +7281,9 @@
         <v>1452.3</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="1" t="s">
-        <v>42</v>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>2017</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>31</v>
@@ -7290,9 +7307,9 @@
         <v>553.41999999999996</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="1" t="s">
-        <v>42</v>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>2017</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>32</v>
@@ -7316,9 +7333,9 @@
         <v>637.19000000000005</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="1" t="s">
-        <v>42</v>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>2017</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>33</v>
